--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -401,7 +401,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:V1000"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="20.14" customWidth="1" style="14" min="1" max="1"/>
     <col width="72" customWidth="1" style="14" min="2" max="2"/>
@@ -431,7 +431,11 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" s="7" t="n"/>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Video URL</t>
+        </is>
+      </c>
       <c r="F1" s="7" t="n"/>
       <c r="G1" s="7" t="n"/>
       <c r="H1" s="7" t="n"/>
@@ -585,7 +589,11 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="7" t="n"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781861957/ftmnag6ckme1glefq8oy.mp4</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="7" t="n"/>
@@ -621,7 +629,11 @@
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
-      <c r="E6" s="7" t="n"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781861960/zb77miqb1izve6tzwryj.mp4</t>
+        </is>
+      </c>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -589,7 +589,11 @@
           <t>2026-06-19 15:47</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n"/>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781861957/ftmnag6ckme1glefq8oy.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -637,7 +637,11 @@
       <c r="C6" s="12" t="n">
         <v>46193.625</v>
       </c>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781861960/zb77miqb1izve6tzwryj.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -679,7 +679,11 @@
       <c r="C7" s="13" t="n">
         <v>46193.75</v>
       </c>
-      <c r="D7" s="9" t="n"/>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865157/yxyda96reg7oc7h44glx.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -721,7 +721,11 @@
       <c r="C8" s="12" t="n">
         <v>46194.41666666666</v>
       </c>
-      <c r="D8" s="6" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865159/sbkypn1palgefbdgj2qo.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -763,7 +763,11 @@
       <c r="C9" s="13" t="n">
         <v>46194.625</v>
       </c>
-      <c r="D9" s="9" t="n"/>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Missed</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865162/p6j4xd9wo6mwiuheh7ue.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -805,7 +805,11 @@
       <c r="C10" s="12" t="n">
         <v>46194.75</v>
       </c>
-      <c r="D10" s="6" t="n"/>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Missed</t>
+        </is>
+      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865165/livws20yuwudad3kcz2g.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -847,7 +847,11 @@
       <c r="C11" s="13" t="n">
         <v>46195.41666666666</v>
       </c>
-      <c r="D11" s="9" t="n"/>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Missed</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865167/xmzkhfymgr3zflxnlgrw.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Missed</t>
+          <t>Posted</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Missed</t>
+          <t>Posted</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Missed</t>
+          <t>Posted</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -889,7 +889,11 @@
       <c r="C12" s="12" t="n">
         <v>46195.625</v>
       </c>
-      <c r="D12" s="6" t="n"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865170/b2uxazarctrxz0nb9z6i.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -931,7 +931,11 @@
       <c r="C13" s="13" t="n">
         <v>46195.75</v>
       </c>
-      <c r="D13" s="9" t="n"/>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865172/oachtdlargjtugvkfmv4.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -973,7 +973,11 @@
       <c r="C14" s="12" t="n">
         <v>46196.41666666666</v>
       </c>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865175/ud92iqstx4ezxwgbfnil.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1015,7 +1015,11 @@
       <c r="C15" s="13" t="n">
         <v>46196.625</v>
       </c>
-      <c r="D15" s="9" t="n"/>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865178/divcmw0bsfckmgygutgs.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1057,7 +1057,11 @@
       <c r="C16" s="12" t="n">
         <v>46196.75</v>
       </c>
-      <c r="D16" s="6" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865180/wed5b6cwyq1xlkvcwnaj.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1099,7 +1099,11 @@
       <c r="C17" s="13" t="n">
         <v>46197.41666666666</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865183/ihthuo3y1sxmvitlcc0u.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1141,7 +1141,11 @@
       <c r="C18" s="12" t="n">
         <v>46197.625</v>
       </c>
-      <c r="D18" s="6" t="n"/>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865185/sxe7hunovlpdazwnjdfw.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1183,7 +1183,11 @@
       <c r="C19" s="13" t="n">
         <v>46197.75</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865188/in0tyd3ggfrpimxinmzl.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1225,7 +1225,11 @@
       <c r="C20" s="12" t="n">
         <v>46198.41666666666</v>
       </c>
-      <c r="D20" s="6" t="n"/>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865191/upro3efogagjdcd8sszy.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1267,7 +1267,11 @@
       <c r="C21" s="13" t="n">
         <v>46198.625</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865193/angcsbshfu1fi1ku27k7.mp4</t>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1309,7 +1309,11 @@
       <c r="C22" s="12" t="n">
         <v>46198.75</v>
       </c>
-      <c r="D22" s="6" t="n"/>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
           <t>https://res.cloudinary.com/dpbkvddbv/video/upload/v1781865196/ad99odyznga4ejtcf0aj.mp4</t>
